--- a/prepare/RodPrep/Output/hotel_data.xlsx
+++ b/prepare/RodPrep/Output/hotel_data.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>hotel_brand_IBIS_BUDGET</t>
+          <t>hotel_brand_ibis_budget</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">

--- a/prepare/RodPrep/Output/hotel_data.xlsx
+++ b/prepare/RodPrep/Output/hotel_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB8"/>
+  <dimension ref="A1:BC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,260 +441,265 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>hotel_brand</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>hotel_adresse_postale_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hotel_adresse_postale_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hotel_code_postal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hotel_city</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hotel_lat</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hotel_lon</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hotel_contrat_signe_annee</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hotel_derniere_reno</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hotel_lobby_derniere_reno</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hotel_nb_chambres</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hotel_to_annuel</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_bas_taux</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_haut_taux</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_assises</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_bouilloire</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_fontaine_a_eau</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_machine_a_cafe</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_micro_ondes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_vitrine_refrigeree</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>hotel_f_b_bar</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>hotel_f_b_minibar</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>hotel_f_b_restaurant</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>hotel_f_b_room_service</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_piscine</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salle_de_sport</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salles_de_reunion</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_spa</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hotel_affaires_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hotel_loisirs_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_amis</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_couples</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_familles</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>hotel_international_pct</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>hotel_national_pct</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_existe_deja</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_de_vente_actuel_metres_lineaires</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_caisse_code_barres</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_frigo_connecte</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_reception</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_snacking_comptoir</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_armoire_connectee</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_caisse_code_barres</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_reception</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>hotel_metres_lineaires_dedies_corner</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_franchise</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_manage</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>hotel_brand_ibis_budget</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>hotel_brand_ibis_styles</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>hotel_brand_mercure</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>hotel_brand_novotel</t>
         </is>
@@ -713,55 +718,57 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>IBIS BUDGET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>58-60 AVENUE DE LA CALIFORNIE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>06200</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>43.689186</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>7.240512</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2003.666666666667</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2020</v>
       </c>
       <c r="K2" t="n">
         <v>2020</v>
       </c>
       <c r="L2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M2" t="n">
         <v>129</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.825</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.755</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.89</v>
       </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -773,7 +780,7 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -791,46 +798,46 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
         <v>4</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
       <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>35.3</v>
       </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
         <v>3</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -845,30 +852,33 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
         <v>6</v>
       </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -885,61 +895,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>IBIS BUDGET</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>23A RUE OBERLIN</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>67000</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>48.591522</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>7.754599</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2020</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2025</v>
       </c>
       <c r="K3" t="n">
         <v>2025</v>
       </c>
       <c r="L3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M3" t="n">
         <v>97</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.7</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.6</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.8</v>
       </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -948,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -969,78 +981,81 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.6</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0.4</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>0.6</v>
       </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
       <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
         <v>2</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
       </c>
       <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
         <v>2</v>
       </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1057,28 +1072,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBIS STYLES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2 AVENUE HEINZ GLOOR</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>95700</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Roissy</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>49.006733</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2015</v>
       </c>
       <c r="J4" t="n">
         <v>2015</v>
@@ -1087,20 +1104,20 @@
         <v>2015</v>
       </c>
       <c r="L4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M4" t="n">
         <v>309</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.95</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.91</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.98</v>
       </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
@@ -1114,19 +1131,19 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1135,84 +1152,87 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>20</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>80</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>30</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>70</v>
       </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
       <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
         <v>5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1229,119 +1249,121 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>MERCURE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>37 PLACE RENÉ CLAIR</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>92100</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>48.833827</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2.256274</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2003.666666666667</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2020</v>
       </c>
       <c r="K5" t="n">
         <v>2020</v>
       </c>
       <c r="L5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M5" t="n">
         <v>191</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.825</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.755</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.89</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
       <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>35.3</v>
       </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
       <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
@@ -1349,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1364,16 +1386,16 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
         <v>6</v>
       </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -1382,9 +1404,12 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1401,52 +1426,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>MERCURE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>3  RUE CAULAINCOURT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>75018</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>48.885048</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2.329923</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>2003.666666666667</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2020</v>
       </c>
       <c r="K6" t="n">
         <v>2020</v>
       </c>
       <c r="L6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M6" t="n">
         <v>305</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.825</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.755</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.89</v>
       </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1458,62 +1485,62 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>35.3</v>
       </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
       <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
@@ -1521,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -1536,27 +1563,30 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6</v>
       </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1573,56 +1603,58 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>NOVOTEL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>1306 ROUTE NATIONALE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>LE DOMAINE DE MEZTIVA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>74120</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Megève</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>6.6190552711</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2003.666666666667</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2020</v>
       </c>
       <c r="K7" t="n">
         <v>2020</v>
       </c>
       <c r="L7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M7" t="n">
         <v>572</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.825</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.755</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.89</v>
       </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1637,35 +1669,35 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -1673,23 +1705,23 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>35.3</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
       <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
@@ -1697,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -1712,16 +1744,16 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
         <v>8</v>
       </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -1733,6 +1765,9 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1749,95 +1784,97 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>NOVOTEL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>61 QUAI DE GRENELLE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>75015</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>48.849778</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.282836</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1976</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2020</v>
       </c>
       <c r="K8" t="n">
         <v>2020</v>
       </c>
       <c r="L8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M8" t="n">
         <v>764</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.825</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.755</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.89</v>
       </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>3</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>36</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
       <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
@@ -1845,28 +1882,28 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>15.2</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>35.3</v>
       </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
       <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -1881,22 +1918,22 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
         <v>7</v>
       </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -1905,6 +1942,9 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
         <v>1</v>
       </c>
     </row>
